--- a/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 17,64</t>
+          <t>4,84; 17,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 19,98</t>
+          <t>6,42; 19,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,82</t>
+          <t>-6,56; 7,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,74</t>
+          <t>-1,33; 5,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,47; 55,43</t>
+          <t>12,54; 53,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 48,38</t>
+          <t>12,89; 47,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 18,58</t>
+          <t>-13,66; 16,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 81,28</t>
+          <t>-12,07; 79,9</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 16,98</t>
+          <t>5,69; 17,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 18,75</t>
+          <t>7,85; 18,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 15,11</t>
+          <t>4,38; 16,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 13,6</t>
+          <t>5,07; 13,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,46; 49,79</t>
+          <t>14,0; 49,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 40,53</t>
+          <t>14,75; 40,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 35,51</t>
+          <t>9,35; 39,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,71; 294,4</t>
+          <t>45,24; 283,65</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 13,45</t>
+          <t>0,83; 13,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 22,94</t>
+          <t>9,15; 22,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 15,9</t>
+          <t>2,18; 15,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 54,57</t>
+          <t>3,55; 57,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 42,14</t>
+          <t>2,02; 42,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,61; 48,69</t>
+          <t>16,56; 46,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 38,02</t>
+          <t>4,47; 35,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,15; 1118,02</t>
+          <t>51,29; 1242,82</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 12,64</t>
+          <t>1,42; 13,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 13,43</t>
+          <t>1,65; 13,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 14,15</t>
+          <t>1,72; 13,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,42</t>
+          <t>-1,5; 3,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 36,63</t>
+          <t>3,65; 40,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 27,94</t>
+          <t>2,68; 27,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 38,93</t>
+          <t>3,95; 37,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 53,85</t>
+          <t>-18,06; 53,81</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,05</t>
+          <t>6,22; 12,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,37</t>
+          <t>9,38; 15,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,4</t>
+          <t>4,22; 10,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 24,67</t>
+          <t>3,52; 24,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,98; 34,01</t>
+          <t>16,08; 34,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,16; 32,31</t>
+          <t>18,43; 31,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 24,6</t>
+          <t>9,23; 24,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,17; 321,31</t>
+          <t>43,21; 380,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,54</t>
+          <t>3,84; 17,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 19,69</t>
+          <t>6,46; 19,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,11</t>
+          <t>-6,57; 7,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,39</t>
+          <t>0,16; 6,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 53,81</t>
+          <t>10,31; 53,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 47,19</t>
+          <t>12,99; 47,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 16,81</t>
+          <t>-13,55; 17,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 79,9</t>
+          <t>0,52; 89,09</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,4</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100,04%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 17,13</t>
+          <t>5,44; 17,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 18,61</t>
+          <t>7,74; 18,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 16,26</t>
+          <t>3,92; 15,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 13,2</t>
+          <t>2,13; 8,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,0; 49,37</t>
+          <t>13,86; 49,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,75; 40,18</t>
+          <t>14,64; 41,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 39,74</t>
+          <t>8,28; 36,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,24; 283,65</t>
+          <t>15,53; 86,4</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,17</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>384,22%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 13,92</t>
+          <t>1,08; 13,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 22,05</t>
+          <t>9,01; 21,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 15,13</t>
+          <t>1,83; 15,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 57,75</t>
+          <t>2,57; 8,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 42,65</t>
+          <t>2,68; 42,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 46,94</t>
+          <t>16,38; 46,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 35,07</t>
+          <t>3,69; 37,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,29; 1242,82</t>
+          <t>30,17; 166,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,54</t>
+          <t>1,21; 12,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 13,11</t>
+          <t>1,51; 13,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 13,65</t>
+          <t>1,95; 14,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,47</t>
+          <t>-0,06; 4,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 40,58</t>
+          <t>3,04; 37,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 27,49</t>
+          <t>2,67; 27,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 37,03</t>
+          <t>4,53; 38,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 53,81</t>
+          <t>-1,92; 68,31</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>115,02%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,09</t>
+          <t>6,13; 12,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,15</t>
+          <t>9,08; 15,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,23</t>
+          <t>3,69; 10,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 24,39</t>
+          <t>2,48; 5,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,08; 34,0</t>
+          <t>15,62; 34,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 31,87</t>
+          <t>17,68; 31,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 24,11</t>
+          <t>8,0; 23,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,21; 380,66</t>
+          <t>26,03; 68,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
